--- a/PTBR/Lang/PTBR/Dialog/Drama/kettle.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/kettle.xlsx
@@ -478,7 +478,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:IX451"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.85" customWidth="1" style="20" min="1" max="1"/>
     <col width="19.85" customWidth="1" style="20" min="2" max="2"/>
@@ -1200,14 +1200,14 @@
       </c>
       <c r="J45" s="26" t="inlineStr">
         <is>
-          <t>あの日…村を訪れた私が見たのは、命あるもの全てが死に絶えた凄惨な光景だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
+          <t>あの日…村を訪れた私を待っていたは、命あるもの全てが死に絶えた凄惨な静寂だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
 あの子は特別な力の元に生まれ、その力は確実に、彼女を取り巻くものたちの運命に影響を与えるだろう。
 もし君たちが望むなら、私とクルイツゥアは出ていくから、いつでも言ってくれ。</t>
         </is>
       </c>
       <c r="K45" s="25" t="inlineStr">
         <is>
-          <t>That day... what I saw when I visited the village was a horrific scene of death where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
+          <t>That day... what awaited me in the village I visited was a horrific silence of death　where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
 She was born under a peculiar power, and that power will undoubtedly affect the fates of those around her.
 If you ever wish us to leave, just say so.</t>
         </is>
@@ -7961,7 +7961,11 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr"/>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="13.8" customHeight="1" s="21">
       <c r="G317" s="25" t="inlineStr">
@@ -7982,7 +7986,11 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr"/>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="113.4" customHeight="1" s="21">
       <c r="G318" s="25" t="inlineStr">
@@ -7998,7 +8006,7 @@
           <t>お、おほん…ということだ、#pcよ。
 この決断は私には荷が重い。お前に任せよう。
 死者の洞窟に赴き、「淀み」を見つけるんだ。そこでイスシズルに渡されたこの瓶を使うか、あるいはファリスさんに渡された「聖水」を使うか…それはお前次第だ、よく考えてくれ。
-…安心しろ、私もついていってやる。お前だけに責任を追わせるのは酷だからな。</t>
+…安心しろ、私もついていってやる。お前だけに責任を負わせるのは酷だからな。</t>
         </is>
       </c>
       <c r="K318" s="28" t="inlineStr">

--- a/PTBR/Lang/PTBR/Dialog/Drama/kettle.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/kettle.xlsx
@@ -478,7 +478,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:IX451"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="8.85" customWidth="1" style="20" min="1" max="1"/>
     <col width="19.85" customWidth="1" style="20" min="2" max="2"/>
@@ -1200,14 +1200,14 @@
       </c>
       <c r="J45" s="26" t="inlineStr">
         <is>
-          <t>あの日…村を訪れた私を待っていたは、命あるもの全てが死に絶えた凄惨な静寂だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
+          <t>あの日…村を訪れた私が見たのは、命あるもの全てが死に絶えた凄惨な光景だった。それが彼女の「力」によるものかはわからない。だが、ロイテル、そして#pc、君たちには覚えておいてほしい。
 あの子は特別な力の元に生まれ、その力は確実に、彼女を取り巻くものたちの運命に影響を与えるだろう。
 もし君たちが望むなら、私とクルイツゥアは出ていくから、いつでも言ってくれ。</t>
         </is>
       </c>
       <c r="K45" s="25" t="inlineStr">
         <is>
-          <t>That day... what awaited me in the village I visited was a horrific silence of death　where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
+          <t>That day... what I saw when I visited the village was a horrific scene of death where every living thing had perished. Whether it was her ‘power’ I cannot say. But, Loytel, and you #pc, remember this. 
 She was born under a peculiar power, and that power will undoubtedly affect the fates of those around her.
 If you ever wish us to leave, just say so.</t>
         </is>
@@ -7961,11 +7961,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
+      <c r="L316" t="inlineStr"/>
     </row>
     <row r="317" ht="13.8" customHeight="1" s="21">
       <c r="G317" s="25" t="inlineStr">
@@ -7986,11 +7982,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
+      <c r="L317" t="inlineStr"/>
     </row>
     <row r="318" ht="113.4" customHeight="1" s="21">
       <c r="G318" s="25" t="inlineStr">
@@ -8006,7 +7998,7 @@
           <t>お、おほん…ということだ、#pcよ。
 この決断は私には荷が重い。お前に任せよう。
 死者の洞窟に赴き、「淀み」を見つけるんだ。そこでイスシズルに渡されたこの瓶を使うか、あるいはファリスさんに渡された「聖水」を使うか…それはお前次第だ、よく考えてくれ。
-…安心しろ、私もついていってやる。お前だけに責任を負わせるのは酷だからな。</t>
+…安心しろ、私もついていってやる。お前だけに責任を追わせるのは酷だからな。</t>
         </is>
       </c>
       <c r="K318" s="28" t="inlineStr">
